--- a/docs/主控板引脚表_G3519.xlsx
+++ b/docs/主控板引脚表_G3519.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2139,681 +2139,677 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>8 路灰度</t>
+          <t>12 路灰度</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>IN1</t>
+          <t>IN1(最左)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>PB27</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>GPIO 输入</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>3.3V 数字</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.11</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>核对</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>固件按旧版 Board_cfg 文档的 12 路定义(物理从左到右 IN1→IN12);旧 PCB 灰度座只直连了 4 路,新板务必 12 路全部接到灰度排针</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>IN2</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>PB12</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>GPIO 输入</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>3.3V 数字</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.9</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>核对</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>同 IN1 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>IN3</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>PB13</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>旧板未见连接</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.40</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>固件为 8 路(IN1-IN8),但旧板灰度座只连了 B09/B17/B19/B26 四路且含固件未用的 B09;新板请按本表连全 8 路</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>IN2</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>同 IN1 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>IN4</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>PB7</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>GPIO 输入</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>3.3V 数字</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.38</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>核对</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>同 IN1 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>IN5</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>B09</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PB9</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>GPIO 输入</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3.3V 数字</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>8路灰度.2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>IN6</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>PB26</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>GPIO 输入</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>3.3V 数字</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>8路灰度.3</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>IN7</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>PB17</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>8路灰度.4</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>IN3</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>B26</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>PB26</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>IN8</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>PB19</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>8路灰度.3</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>8路灰度.6</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>IN4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>PB19</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>IN9</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>B21</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>PB21</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>8路灰度.6</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>IN5</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>B21</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>PB21</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.28</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>核对</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>同 IN1 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>IN10</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>PB10</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>旧板未见连接</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.26</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>IN6</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>PB10</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>IN11</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>PB11</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>旧板未见连接</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.24</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>IN7</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>PB11</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>12 路灰度</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>IN12(最右)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>PB24</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>旧板未见连接</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>拓展板.22</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>8 路灰度</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>IN8</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>B24</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>PB24</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>GPIO 输入</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>3.3V 数字</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>旧板未见连接</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>核对</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>同 IN1 备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>已删除/释放</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>旧陀螺仪 I2C0 SDA</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>A28(废)</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>PA28</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>陀螺仪.2</t>
-        </is>
-      </c>
-      <c r="K38" s="11" t="inlineStr">
-        <is>
-          <t>删除</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="inlineStr">
-        <is>
-          <t>I2C_IMU 已随 MPU6050 移除,引脚释放</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>已删除/释放</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>旧陀螺仪 I2C0 SCL</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>A31(废)</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>PA31</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>陀螺仪.3</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr">
-        <is>
-          <t>删除</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>已删除/释放</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>旧左轮编码器 B 相</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>B20(废)</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>PB20</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>U33.4</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>删除</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr">
-        <is>
-          <t>软件中断编码器废弃,引脚释放可作扩展</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>已删除/释放</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>旧右轮编码器 A 相</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>B14(废)</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>PB14</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>U34.3</t>
-        </is>
-      </c>
-      <c r="K41" s="11" t="inlineStr">
-        <is>
-          <t>删除</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>同上</t>
         </is>
       </c>
     </row>
@@ -2828,48 +2824,280 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
+          <t>旧陀螺仪 I2C0 SDA</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>A28(废)</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>PA28</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>陀螺仪.2</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>I2C_IMU 已随 MPU6050 移除,引脚释放</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>已删除/释放</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>旧陀螺仪 I2C0 SCL</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>A31(废)</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>PA31</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>陀螺仪.3</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>已删除/释放</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>旧左轮编码器 B 相</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>B20(废)</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>PB20</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>U33.4</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>软件中断编码器废弃,引脚释放可作扩展</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>已删除/释放</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>旧右轮编码器 A 相</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>B14(废)</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>PB14</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>U34.3</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>已删除/释放</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
           <t>旧右轮编码器 B 相</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>B00(废)</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>PB0</t>
         </is>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F46" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>U34.4</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -3071,17 +3299,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>8 路灰度座</t>
+          <t>12 路灰度座</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>旧板仅连 B09/B17/B19/B26</t>
+          <t>旧 PCB 灰度座仅直连 4 路(B09/B26/B17/B19)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>按总表连全 8 路:PB13/PB17/PB26/PB19/PB21/PB10/PB11/PB24</t>
+          <t>固件已按 12 路配置,从左到右 IN1→IN12 = PB27/PB12/PB13/PB7/PB9/PB26/PB17/PB19/PB21/PB10/PB11/PB24,新板 12 路全接</t>
         </is>
       </c>
     </row>

--- a/docs/主控板引脚表_G3519.xlsx
+++ b/docs/主控板引脚表_G3519.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -99,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,7 +114,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,22 +129,28 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,21 +518,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,40 +559,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>固件宏名(define)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>MCU引脚</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LQFP-100脚号</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>复用功能</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>电气要求</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>旧板连接参考</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>变更状态</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -602,38 +624,43 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>—(器件固定功能)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>NRST</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>NRST</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>RC 复位/按键</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>U2.35</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -656,38 +683,43 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>—(DEBUGSS)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>PA20</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>DEBUGSS.SWCLK</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>核心板调试口</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -710,38 +742,43 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—(DEBUGSS)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>PA19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>DEBUGSS.SWDIO</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>双向</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>核心板调试口</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -762,152 +799,167 @@
           <t>B22</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_STATUS_LED_PIN_22_PIN</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PB22</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>GPIO 输出</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>内部下拉</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>LED1 经 R33</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>主机链路(无线串口/VOFA)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>UART0 发送</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>A10</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_UART_HOST_LINK_TX_PIN</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>PA10</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>UART0.TX</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>旧板 A10 标 OFF 未连!</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>固件主机链路一直是 PA10/PA11;旧板"无线串口0"座接的是 A00/A01(PA0/PA1),两者对不上。新板必须把无线串口座 RX 接 PA10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>主机链路(无线串口/VOFA)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>UART0 接收</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_UART_HOST_LINK_RX_PIN</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>PA11</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>UART0.RX</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>旧板 A11 标 OFF 未连!</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>同上:无线串口座 TX 接 PA11</t>
         </is>
@@ -932,40 +984,45 @@
           <t>A08</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_UART_VISION_TX_PIN</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>PA8</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>UART1.TX</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>视觉模块.4</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -986,40 +1043,45 @@
           <t>A09</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_UART_VISION_RX_PIN</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>PA9</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>UART1.RX</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>视觉模块.3</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1040,40 +1102,45 @@
           <t>B15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_UART_STEPPER_BUS_TX_PIN</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>PB15</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>UART7.TX</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>步进串口.4 / 上端步进.3 / CN2.3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>引脚和网络名都不变;仅软件外设实例由 UART2 改为 UART7(G3519 没有 UART2),原理图无需动作</t>
         </is>
@@ -1098,156 +1165,171 @@
           <t>B16</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_UART_STEPPER_BUS_RX_PIN</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>PB16</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>UART7.RX</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>步进串口.3 / 上端步进.4 / CN2.4</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>新陀螺仪(UART)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>UART3 发送</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>A26</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_TX_PIN</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>PA26</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>UART3.TX</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>旧接"调试串口(3V3)".4</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>重定义</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>换用串口陀螺仪:建议陀螺仪 4P 座重定义为 5V/GND/PA26(TX→IMU RX)/PA25(RX←IMU TX)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>新陀螺仪(UART)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>UART3 接收</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>A25</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_RX_PIN</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>PA25</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>UART3.RX</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>3.3V TTL 230400</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>旧接"调试串口(3V3)".3</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>重定义</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1272,40 +1354,45 @@
           <t>A30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_I2C_AUX_SDA_PIN</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>PA30</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>I2C1.SDA</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>双向</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>外部上拉 4.7k, Fast 400k</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>OLED按键.5</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1326,40 +1413,45 @@
           <t>A29</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_I2C_AUX_SCL_PIN</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>PA29</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>I2C1.SCL</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>双向</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>外部上拉 4.7k, Fast 400k</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>OLED按键.6</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1380,40 +1472,45 @@
           <t>B04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K1_PIN</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>PB4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入/下降沿中断</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>内部上拉,按下接地</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>OLED按键.1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1434,40 +1531,45 @@
           <t>B05</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K2_PIN</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>PB5</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入/下降沿中断</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>内部上拉,按下接地</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>OLED按键.2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1488,40 +1590,45 @@
           <t>B25</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K3_PIN</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>PB25</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入/下降沿中断</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>内部上拉,按下接地</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>OLED按键.3</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1542,40 +1649,45 @@
           <t>A14</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K4_PIN</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>PA14</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入/下降沿中断</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>内部上拉,按下接地</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>OLED按键.4</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1583,7 +1695,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>编码器-左轮(硬件QEI)</t>
+          <t>编码器-左轮(硬件QEI, TIMG8)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1596,214 +1708,234 @@
           <t>A07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHA_PIN</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>PA7</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>TIMG8.CCP0 (QEI PHA)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>3.3V 方波</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>U33.3(原 A07,不变)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>左轮编码器升级为 TIMG8 硬件正交解码,A 相沿用 PA7</t>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>左轮编码器升级为 TIMG8 硬件正交解码(QEI_LEFT_INST),A 相沿用 PA7</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>编码器-左轮(硬件QEI)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>编码器-左轮(硬件QEI, TIMG8)</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>左轮 B 相</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHB_PIN</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>PA6</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="G21" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>TIMG8.CCP1 (QEI PHB)</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>3.3V 方波</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>U33.4(原 B20)</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>变更</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>★改线:U33.4 由 PB20 改接 PA6</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>编码器-右轮(硬件QEI)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>编码器-右轮(硬件QEI, TIMG9)</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>右轮 A 相</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHA_PIN</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>PA3</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="G22" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>TIMG9.CCP0 (QEI PHA)</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>3.3V 方波</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>U34.3(原 B14)</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>变更</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>★改线:U34.3 由 PB14 改接 PA3</t>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>★改线:U34.3 由 PB14 改接 PA3(QEI_RIGHT_INST)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>编码器-右轮(硬件QEI)</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>编码器-右轮(硬件QEI, TIMG9)</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>右轮 B 相</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHB_PIN</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>PA2</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="G23" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>TIMG9.CCP1 (QEI PHB)</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>3.3V 方波</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>U34.4(原 B00)</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>变更</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>★改线:U34.4 由 PB0 改接 PA2(旧网表 A02 标 OFF,现启用)</t>
         </is>
@@ -1828,40 +1960,45 @@
           <t>A13</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_AIN1_PIN</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>PA13</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>GPIO 输出</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>H2.7</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1882,40 +2019,45 @@
           <t>A12</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_AIN2_PIN</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>PA12</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>GPIO 输出</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>H2.6</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1936,40 +2078,45 @@
           <t>A17</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_BIN1_PIN</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>PA17</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>GPIO 输出</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>H2.4</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1990,40 +2137,45 @@
           <t>A24</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_BIN2_PIN</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>PA24</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>GPIO 输出</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>H2.3</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2044,40 +2196,49 @@
           <t>A22</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_PWM_DRIVE_LEFT_C1_PIN</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>PA22</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>TIMA0.CCP1</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>H2.2</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>PWM_DRIVE_LEFT_INST=TIMA0</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2098,268 +2259,297 @@
           <t>B02</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_PWM_DRIVE_RIGHT_C0_PIN</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>PB2</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>TIMA1.CCP0</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>H2.8</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>PWM_DRIVE_RIGHT_INST=TIMA1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>IN1(最左)</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>B27</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN1_PIN</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>PB27</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>拓展板.11</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>固件按旧版 Board_cfg 文档的 12 路定义(物理从左到右 IN1→IN12);旧 PCB 灰度座只直连了 4 路,新板务必 12 路全部接到灰度排针</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>IN2</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN2_PIN</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>PB12</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>拓展板.9</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>IN3</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN3_PIN</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>PB13</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>拓展板.40</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>IN4</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>B07</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN4_PIN</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>PB7</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>拓展板.38</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
@@ -2384,40 +2574,45 @@
           <t>B09</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN5_PIN</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>PB9</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>8路灰度.2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2438,40 +2633,45 @@
           <t>B26</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN6_PIN</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>PB26</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>8路灰度.3</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2492,40 +2692,45 @@
           <t>B17</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN7_PIN</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>PB17</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>8路灰度.4</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2546,558 +2751,608 @@
           <t>B19</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN8_PIN</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>PB19</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>8路灰度.6</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>不变</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>IN9</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>B21</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN9_PIN</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>PB21</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>拓展板.28</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>IN10</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN10_PIN</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>PB10</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>拓展板.26</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>IN11</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN11_PIN</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>PB11</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>拓展板.24</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>12 路灰度</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>IN12(最右)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>B24</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN12_PIN</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>PB24</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>GPIO 输入</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>3.3V 数字</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>拓展板.22</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>核对</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr">
         <is>
           <t>同 IN1 备注</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>已删除/释放</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>旧陀螺仪 I2C0 SDA</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>A28(废)</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>—(已删除)</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>PA28</t>
         </is>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="G42" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="K42" s="16" t="inlineStr">
         <is>
           <t>陀螺仪.2</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="L42" s="15" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="M42" s="16" t="inlineStr">
         <is>
           <t>I2C_IMU 已随 MPU6050 移除,引脚释放</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>已删除/释放</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>旧陀螺仪 I2C0 SCL</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>A31(废)</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>—(已删除)</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>PA31</t>
         </is>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="G43" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="I43" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="J43" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="K43" s="16" t="inlineStr">
         <is>
           <t>陀螺仪.3</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="L43" s="15" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="M43" s="16" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
+      <c r="A44" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>已删除/释放</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>旧左轮编码器 B 相</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>B20(废)</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>—(已删除)</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>PB20</t>
         </is>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="G44" s="15" t="n">
         <v>82</v>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="K44" s="16" t="inlineStr">
         <is>
           <t>U33.4</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="M44" s="16" t="inlineStr">
         <is>
           <t>软件中断编码器废弃,引脚释放可作扩展</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>已删除/释放</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>旧右轮编码器 A 相</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>B14(废)</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>—(已删除)</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>PB14</t>
         </is>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="G45" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="K45" s="16" t="inlineStr">
         <is>
           <t>U34.3</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="L45" s="15" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="M45" s="16" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>已删除/释放</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>旧右轮编码器 B 相</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>B00(废)</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>—(已删除)</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>PB0</t>
         </is>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="G46" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="K46" s="16" t="inlineStr">
         <is>
           <t>U34.4</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>删除</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="M46" s="16" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -3152,162 +3407,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>改线</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>U33.4(左轮编码器 B 相)</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>PB20 → PA6(LQFP-100 第 19 脚)</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>左轮升级 TIMG8 硬件 QEI</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>改线</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>U34.3(右轮编码器 A 相)</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>PB14 → PA3(第 16 脚)</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>右轮升级 TIMG9 硬件 QEI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>改线</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>U34.4(右轮编码器 B 相)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>PB0 → PA2(第 15 脚)</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>接口重定义</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>陀螺仪 4P 座</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>原 I2C(PA28/PA31)→ 串口 PA26(TX)/PA25(RX)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>换串口陀螺仪,I2C_IMU 已删除</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>画板前核对</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>无线串口0 座(主机链路)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>旧板接 A00/A01,固件用 PA10/PA11(A10/A11 旧板标 OFF)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>两者不一致,新板必须接 PA10(TX)/PA11(RX)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>画板前核对</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>12 路灰度座</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>旧 PCB 灰度座仅直连 4 路(B09/B26/B17/B19)</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>固件已按 12 路配置,从左到右 IN1→IN12 = PB27/PB12/PB13/PB7/PB9/PB26/PB17/PB19/PB21/PB10/PB11/PB24,新板 12 路全接</t>
         </is>
